--- a/Providers_Ready_To_Import_Clean.xlsx
+++ b/Providers_Ready_To_Import_Clean.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tba_waad_system-main_success\tba_waad_system-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07746E28-3327-422C-9F9A-90048A0F8E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -202,9 +208,6 @@
     <t>CLINIC_DEN</t>
   </si>
   <si>
-    <t>Tripoli</t>
-  </si>
-  <si>
     <t>ضمن الشبكة</t>
   </si>
   <si>
@@ -212,17 +215,20 @@
   </si>
   <si>
     <t>نعم</t>
+  </si>
+  <si>
+    <t>بنغازي</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -230,7 +236,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -281,13 +287,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -325,7 +339,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -359,6 +373,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -393,9 +408,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -568,11 +584,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="17.69921875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,7 +638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -627,19 +646,19 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -647,19 +666,19 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -667,19 +686,19 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -687,19 +706,19 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -707,19 +726,19 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -727,19 +746,19 @@
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -747,19 +766,19 @@
         <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -767,19 +786,19 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -787,19 +806,19 @@
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -807,19 +826,19 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -827,19 +846,19 @@
         <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -847,19 +866,19 @@
         <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -867,19 +886,19 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -887,19 +906,19 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -907,19 +926,19 @@
         <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -927,19 +946,19 @@
         <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -947,19 +966,19 @@
         <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -967,19 +986,19 @@
         <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -987,19 +1006,19 @@
         <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1007,19 +1026,19 @@
         <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1027,19 +1046,19 @@
         <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1047,19 +1066,19 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1067,19 +1086,19 @@
         <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1087,19 +1106,19 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1107,19 +1126,19 @@
         <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1127,19 +1146,19 @@
         <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1147,19 +1166,19 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1167,19 +1186,19 @@
         <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -1187,19 +1206,19 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>44</v>
       </c>
@@ -1207,19 +1226,19 @@
         <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>45</v>
       </c>
@@ -1227,19 +1246,19 @@
         <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -1247,19 +1266,19 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -1267,19 +1286,19 @@
         <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -1287,19 +1306,19 @@
         <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -1307,19 +1326,19 @@
         <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -1327,19 +1346,19 @@
         <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -1347,19 +1366,19 @@
         <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -1367,19 +1386,19 @@
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -1387,16 +1406,16 @@
         <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
